--- a/output/pdf_financials_xlsx/ESK.xlsx
+++ b/output/pdf_financials_xlsx/ESK.xlsx
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.634042</v>
+        <v>-1.634042</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>13.981393</v>
+        <v>-13.981393</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-3.245896</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.634042</v>
+        <v>-1.634042</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>13.981393</v>
+        <v>-13.981393</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-2.318096</v>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.634042</v>
+        <v>-1.634042</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>13.981393</v>
+        <v>-13.981393</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-2.318096</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>81.7021</v>
+        <v>-81.7021</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>73.586279</v>
+        <v>-73.586279</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.634042</v>
+        <v>-1.634042</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>13.981393</v>
+        <v>-13.981393</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.245896</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.634042</v>
+        <v>-1.634042</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>13.981393</v>
+        <v>-13.981393</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.245896</v>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-28.58378703445828</v>
@@ -6238,55 +6238,55 @@
         <v>5.461109</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.058109</v>
+        <v>0.570474</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>6.476409</v>
+        <v>0.9595</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.787857</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.66105</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.82306</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.7451950000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.72479</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.96415</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.251254</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.1656</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.468836</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>11.413593</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>12.083662</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.161913</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>14.728845</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>13.512756</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>6.028724</v>
       </c>
     </row>
     <row r="93">
@@ -7773,13 +7773,13 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.1475</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.020935</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -10528,7 +10528,11 @@
           <t>Reserves (notes 14 and 15)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11362,7 +11366,11 @@
           <t>Reserves (notes 13 and 14)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -12396,7 +12404,11 @@
           <t>Reserves (notes 15 &amp; 16)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12812,7 +12824,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -14332,7 +14348,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -14842,7 +14862,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -15476,7 +15500,11 @@
           <t>Reserves (note 13)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -16182,7 +16210,11 @@
           <t>Reserves (note 12)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -18280,7 +18312,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -36716,7 +36752,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -57234,10 +57274,10 @@
         </is>
       </c>
       <c r="E465" s="5" t="n">
-        <v>1.634042</v>
+        <v>-1.634042</v>
       </c>
       <c r="F465" s="5" t="n">
-        <v>13.981393</v>
+        <v>-13.981393</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ESK.xlsx
+++ b/output/pdf_financials_xlsx/ESK.xlsx
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.095413</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06936</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.020413</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001382</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000754</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000664</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000662</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000182</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
@@ -1125,28 +1125,28 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000147</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.010561</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.01726</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.06715400000000001</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.03886</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.077711</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.084311</v>
       </c>
     </row>
     <row r="13">
@@ -2166,28 +2166,28 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.634042</v>
+        <v>-1.538629</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.981393</v>
+        <v>-13.912033</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.245896</v>
+        <v>-3.266309</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.163005</v>
+        <v>-1.164387</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.462354</v>
+        <v>-0.463108</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.506462</v>
+        <v>-0.507126</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.559136</v>
+        <v>-0.559798</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.509885</v>
+        <v>-0.510067</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2200,28 +2200,28 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.693671</v>
+        <v>-0.693676</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.304786</v>
+        <v>-1.304933</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-14.181357</v>
+        <v>-14.191918</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-18.891069</v>
+        <v>-18.908329</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-18.267594</v>
+        <v>-18.334748</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.797773</v>
+        <v>-2.836633</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-2.085952</v>
+        <v>-2.163663</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-1.236297</v>
+        <v>-1.320608</v>
       </c>
     </row>
     <row r="28">
@@ -2296,28 +2296,28 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.634042</v>
+        <v>-1.538629</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.981393</v>
+        <v>-13.912033</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.245896</v>
+        <v>-3.266309</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.163005</v>
+        <v>-1.164387</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.462354</v>
+        <v>-0.463108</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.501575</v>
+        <v>-0.502239</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.559136</v>
+        <v>-0.559798</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.509885</v>
+        <v>-0.510067</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2330,28 +2330,28 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.693671</v>
+        <v>-0.693676</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.304786</v>
+        <v>-1.304933</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-14.181357</v>
+        <v>-14.191918</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-18.891069</v>
+        <v>-18.908329</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-18.267594</v>
+        <v>-18.334748</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.797773</v>
+        <v>-2.836633</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-2.085952</v>
+        <v>-2.163663</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-1.236297</v>
+        <v>-1.320608</v>
       </c>
     </row>
     <row r="30">
@@ -2639,28 +2639,28 @@
         <v>0.011559</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.012052</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.009537</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.029797</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.007501</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.113696</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.165634</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.060693</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.177307</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>14.473006</v>
@@ -2761,28 +2761,28 @@
         <v>0.011559</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.012052</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.009537</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.029797</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.007501</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.113696</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.165634</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.060693</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.177307</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>14.473006</v>
@@ -3493,28 +3493,28 @@
         <v>0.027508</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.019653</v>
+        <v>0.007601</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.014369</v>
+        <v>0.004832</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.034629</v>
+        <v>0.004832</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.012333</v>
+        <v>0.004832</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.11942</v>
+        <v>0.005724</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.175509</v>
+        <v>0.009875</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.07638</v>
+        <v>0.015687</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.186581</v>
+        <v>0.009273999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.884462</v>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -47572,7 +47572,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -54634,7 +54634,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E440" s="5" t="n">

--- a/output/pdf_financials_xlsx/ESK.xlsx
+++ b/output/pdf_financials_xlsx/ESK.xlsx
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.356327</v>
+        <v>0.446327</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.67488</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-1.634042</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-13.981393</v>
+        <v>1.799</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-3.245896</v>
@@ -1391,13 +1391,13 @@
         <v>-1.304786</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-14.181357</v>
+        <v>-14.155134</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-18.891069</v>
+        <v>-18.885148</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-18.267594</v>
+        <v>-18.223512</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-2.797773</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.442042</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-15.780393</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.1179</v>
+        <v>-0.1179</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.001458</v>
+        <v>-0.001458</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1456,13 +1456,13 @@
         <v>-0</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.026223</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.005921</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.044082</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>-0</v>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.538629</v>
+        <v>0.903413</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.912033</v>
+        <v>1.86836</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.266309</v>
@@ -2206,13 +2206,13 @@
         <v>-1.304933</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-14.191918</v>
+        <v>-14.165695</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-18.908329</v>
+        <v>-18.902408</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-18.334748</v>
+        <v>-18.290666</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-2.836633</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.538629</v>
+        <v>0.903413</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.912033</v>
+        <v>1.86836</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.266309</v>
@@ -2336,13 +2336,13 @@
         <v>-1.304933</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-14.191918</v>
+        <v>-14.165695</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-18.908329</v>
+        <v>-18.902408</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-18.334748</v>
+        <v>-18.290666</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-2.836633</v>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>302.2329207920792</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>877.1758198999445</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-28.58378703445828</v>
@@ -2498,13 +2498,13 @@
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.1852543395209116</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.03135267989427459</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2418962930965228</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0</v>
@@ -7291,46 +7291,46 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.001689</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.00175</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.001812</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.001878</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.001945</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.002015</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.002087</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.002162</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.002242</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.064182</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.317627</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.005503</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.004693</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.00293</v>
       </c>
     </row>
     <row r="111">
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014828</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7376,16 +7376,16 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.08096299999999999</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.048984</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.09455</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.077513</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014828</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8815,16 +8815,16 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.08096299999999999</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.048984</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.09455</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.077513</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
         <v>-0.335857</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.443204</v>
+        <v>-2.458032</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.673603</v>
@@ -8876,16 +8876,16 @@
         <v>-0.418386</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-6.171755</v>
+        <v>-6.252718</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-15.442691</v>
+        <v>-15.491675</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-14.768941</v>
+        <v>-14.863491</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-0.107114</v>
+        <v>-0.184627</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>-0.899996</v>
@@ -21256,7 +21256,11 @@
           <t>Accretion (notes 9)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -23738,7 +23742,11 @@
           <t>Purchase of equipment (note 4)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -24268,7 +24276,11 @@
           <t>Accretion (notes 10 and 12)</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -24688,7 +24700,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -25196,7 +25212,11 @@
           <t>Accretion (note 10 and 13)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -26744,7 +26764,11 @@
           <t>Accretion (note 8)</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -33342,7 +33366,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -36436,7 +36464,11 @@
           <t>Accretion (note 9)</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -38766,7 +38798,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -39612,7 +39648,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -41400,7 +41440,11 @@
           <t>Purchase of equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -41824,7 +41868,11 @@
           <t>Proceeds from private placement (Note 8)</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -50150,7 +50198,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -52742,7 +52794,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -53364,7 +53420,11 @@
           <t>Income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -53894,7 +53954,11 @@
           <t>Income tax recovery (note 18)</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -54948,7 +55012,11 @@
           <t>LOSS BEFORE INCOME TAX RECOVERY</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E443" s="5" t="n">
         <v>2.442042</v>
       </c>
@@ -56102,7 +56170,11 @@
           <t>Directors fees (Note 13)</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E454" s="5" t="n">
         <v>0.09</v>
       </c>
